--- a/outputs/domain-availability-export/Domain-Availability-Report.xlsx
+++ b/outputs/domain-availability-export/Domain-Availability-Report.xlsx
@@ -2,9 +2,9 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Summary" sheetId="1" r:id="Ra3e20f95313545d2"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="All Results" sheetId="2" r:id="R2d62f409b99f457f"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Potentially Available" sheetId="3" r:id="R5c575aabc59d4ecd"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Summary" sheetId="1" r:id="Rcc3842b15bea4e79"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="All Results" sheetId="2" r:id="R98fe7efb553e4908"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Potentially Available" sheetId="3" r:id="Rc0e391ef886542c6"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -12,7 +12,7 @@
 <file path=xl/comments1.xml><?xml version="1.0" encoding="utf-8"?>
 <x:comments xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:authors>
-    <x:author>tc={CAFA6AC9-2698-D5F6-A422-CC4E902E3E23}</x:author>
+    <x:author>tc={5A7957A4-7D45-AF62-43BC-40DF727FEF9D}</x:author>
   </x:authors>
   <x:commentList>
     <x:comment ref="A21" authorId="0">
@@ -548,7 +548,7 @@
 
 <file path=xl/persons/person.xml><?xml version="1.0" encoding="utf-8"?>
 <xltc:personList xmlns:xltc="http://schemas.microsoft.com/office/spreadsheetml/2018/threadedcomments">
-  <xltc:person displayName="User" id="{68F238F9-DBA9-4BF6-A8CE-D52DD89E5691}"/>
+  <xltc:person displayName="User" id="{28A8194D-3DCB-4F81-92C4-FCAB693C092E}"/>
 </xltc:personList>
 </file>
 
@@ -781,7 +781,7 @@
 
 <file path=xl/threadedcomments/threadedcomment.xml><?xml version="1.0" encoding="utf-8"?>
 <xltc:ThreadedComments xmlns:xltc="http://schemas.microsoft.com/office/spreadsheetml/2018/threadedcomments">
-  <xltc:threadedComment ref="A21" dT="2026-07-24T23:39:17.389" personId="{68F238F9-DBA9-4BF6-A8CE-D52DD89E5691}" id="{CAFA6AC9-2698-D5F6-A422-CC4E902E3E23}">
+  <xltc:threadedComment ref="A21" dT="2026-07-24T23:40:02.862" personId="{28A8194D-3DCB-4F81-92C4-FCAB693C092E}" id="{5A7957A4-7D45-AF62-43BC-40DF727FEF9D}">
     <xltc:text>Domain results are time-sensitive. Recheck any shortlisted domain with an accredited registrar immediately before purchase.</xltc:text>
   </xltc:threadedComment>
 </xltc:ThreadedComments>
@@ -852,11 +852,11 @@
     </x:row>
     <x:row r="7">
       <x:c r="A7" s="20" t="str">
-        <x:v>Names requiring further verification</x:v>
+        <x:v>Unconfirmed domain checks</x:v>
       </x:c>
       <x:c r="B7" s="31" t="n">
-        <x:f>COUNTIF('All Results'!$C$5:$C$414,"Unconfirmed*")+COUNTIF('All Results'!$E$5:$E$414,"Unconfirmed*")+COUNTIF('All Results'!$G$5:$G$414,"Unconfirmed*")</x:f>
-        <x:v>0</x:v>
+        <x:f>SUM(D11:D13)</x:f>
+        <x:v>693</x:v>
       </x:c>
     </x:row>
     <x:row r="10">
@@ -982,7 +982,7 @@
     <x:mergeCell ref="A22:F22"/>
   </x:mergeCells>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <x:legacyDrawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rbb2486b4ea7d423c"/>
+  <x:legacyDrawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R561ab94daa5740b2"/>
 </x:worksheet>
 </file>
 
@@ -13579,7 +13579,7 @@
   </x:conditionalFormatting>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R9307acdb1e9b4c31"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Ra103a4f02482454b"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -19577,7 +19577,7 @@
   </x:conditionalFormatting>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R54fd7c7608164bf7"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Ra425313edb1c40ea"/>
   </x:tableParts>
 </x:worksheet>
 </file>